--- a/docs/_baseline/amphibian_report.xlsx
+++ b/docs/_baseline/amphibian_report.xlsx
@@ -1,14 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <bookViews>
-    <workbookView activeTab="3"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="조사개황" state="visible" r:id="rId1"/>
     <sheet sheetId="2" name="출현종" state="visible" r:id="rId2"/>
     <sheet sheetId="3" name="출현종요약" state="visible" r:id="rId3"/>
-    <sheet sheetId="4" name="License" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">출현종!$A$3:$V$8</definedName>
@@ -18,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87">
   <si>
     <t>양서파충류 조사결과 — 조사개황</t>
   </si>
@@ -143,7 +139,7 @@
     <t>장지뱀과</t>
   </si>
   <si>
-    <t>국명</t>
+    <t>일반명</t>
   </si>
   <si>
     <t>참개구리</t>
@@ -279,9 +275,6 @@
   </si>
   <si>
     <t>기타 합계</t>
-  </si>
-  <si>
-    <t>Thank you for using version 2026.2.519.80 of Telerik Document Processing Libraries. License validation couldn't run, possibly due to a missing Telerik.Licensing NuGet package reference to BaselineGen. See documentation for setup. Learn more about Telerik Document Processing Libraries licensing https://docs.telerik.com/devtools/document-processing/distribution-and-licensing/license-key</t>
   </si>
 </sst>
 </file>
@@ -289,7 +282,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <b val="false"/>
       <i val="false"/>
@@ -355,15 +348,6 @@
       <color rgb="FFE53935"/>
       <name val="맑은 고딕"/>
     </font>
-    <font>
-      <b val="false"/>
-      <i val="false"/>
-      <u val="none"/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -396,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true"/>
     <xf numFmtId="0" fontId="1" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="2" borderId="0" xfId="0" applyFont="true"/>
@@ -411,7 +395,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="7" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="8" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -531,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr customHeight="false" defaultColWidth="9.28125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" bestFit="false" customWidth="true" width="28.57421875" hidden="false" outlineLevel="0"/>
@@ -687,6 +670,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
@@ -1404,19 +1391,4 @@
   <autoFilter ref="A3:U4"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr customHeight="false" defaultColWidth="9.28125" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
-</worksheet>
 </file>
--- a/docs/_baseline/amphibian_report.xlsx
+++ b/docs/_baseline/amphibian_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85">
   <si>
     <t>양서파충류 조사결과 — 조사개황</t>
   </si>
@@ -43,9 +43,6 @@
     <t>하천명</t>
   </si>
   <si>
-    <t>하천유형</t>
-  </si>
-  <si>
     <t>사업장</t>
   </si>
   <si>
@@ -67,7 +64,7 @@
     <t>조사자</t>
   </si>
   <si>
-    <t>※ 관리자 테이블에 대권역·중권역·하천유형·조사기관 컬럼이 없어 일괄입력 시에는 해당 열이 비워진다.</t>
+    <t>※ 관리자 테이블에 대권역·중권역·조사기관 컬럼이 없어 일괄입력 시에는 해당 열이 비워진다.</t>
   </si>
   <si>
     <t>방류하천</t>
@@ -83,9 +80,6 @@
   </si>
   <si>
     <t>곡교천</t>
-  </si>
-  <si>
-    <t>평지형</t>
   </si>
   <si>
     <t>온양</t>
@@ -514,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr customHeight="false" defaultColWidth="9.28125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" bestFit="false" customWidth="true" width="28.57421875" hidden="false" outlineLevel="0"/>
@@ -546,7 +540,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -562,7 +556,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -578,7 +572,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -586,7 +580,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -594,7 +588,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -602,7 +596,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -610,15 +604,15 @@
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>25</v>
+      <c r="B14" s="2" t="n">
+        <v>36.763081</v>
       </c>
     </row>
     <row r="15">
@@ -626,15 +620,15 @@
         <v>12</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>36.763081</v>
+        <v>127.090606</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>127.090606</v>
+      <c r="B16" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -642,7 +636,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -650,30 +644,22 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2"/>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="A21" s="2"/>
       <c r="B21" s="2"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.6999999999999998" right="0.6999999999999998" top="0.75"/>
@@ -704,7 +690,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -754,102 +740,102 @@
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>32</v>
-      </c>
       <c r="F3" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>2</v>
       </c>
       <c r="J3" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="L3" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M3" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="P3" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="Q3" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="R3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="T3" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="Q3" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="T3" s="6" t="s">
+      <c r="U3" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="U3" s="6" t="s">
-        <v>66</v>
-      </c>
       <c r="V3" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K4" s="7" t="n">
         <v>12</v>
@@ -871,43 +857,43 @@
         <v>127.090606</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="V4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>8</v>
@@ -929,43 +915,43 @@
         <v>127.090606</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="V5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>1</v>
@@ -985,45 +971,45 @@
         <v>127.090606</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>2</v>
@@ -1045,45 +1031,45 @@
         <v>127.090606</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="V7" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="7" t="n">
@@ -1103,10 +1089,10 @@
         <v>127.090606</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="V8" s="2"/>
     </row>
@@ -1138,7 +1124,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1186,16 +1172,16 @@
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>11</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>4</v>
@@ -1204,69 +1190,69 @@
         <v>8</v>
       </c>
       <c r="G3" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="K3" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="L3" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="M3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="N3" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="M3" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="N3" s="6" t="s">
+      <c r="P3" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="Q3" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="R3" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="S3" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="T3" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="U3" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="U3" s="6" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>46156</v>
@@ -1284,10 +1270,10 @@
         <v>1</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N4" s="7" t="n">
         <v>3</v>
@@ -1339,7 +1325,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1364,7 +1350,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
